--- a/nr-update-valueset/ig/StructureDefinition-as-ext-data-trace.xlsx
+++ b/nr-update-valueset/ig/StructureDefinition-as-ext-data-trace.xlsx
@@ -57,13 +57,13 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T14:32:05+00:00</t>
+    <t>2024-03-06T16:49:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
   </si>
   <si>
-    <t>ANS</t>
+    <t>Agence du Numérique en Santé (ANS) - 2-10 Rue d'Oradour-sur-Glane, 75015 Paris</t>
   </si>
   <si>
     <t>Contact</t>

--- a/nr-update-valueset/ig/StructureDefinition-as-ext-data-trace.xlsx
+++ b/nr-update-valueset/ig/StructureDefinition-as-ext-data-trace.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-06T16:49:12+00:00</t>
+    <t>2024-03-07T12:17:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -431,7 +431,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/type-systeme-information-vs</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/ValueSet/as-vs-type-systeme-information</t>
   </si>
   <si>
     <t>base64Binary

--- a/nr-update-valueset/ig/StructureDefinition-as-ext-data-trace.xlsx
+++ b/nr-update-valueset/ig/StructureDefinition-as-ext-data-trace.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-07T12:17:43+00:00</t>
+    <t>2024-03-07T12:27:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
